--- a/artfynd/A 25717-2024 artfynd.xlsx
+++ b/artfynd/A 25717-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98822806</v>
+        <v>98822974</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älgflotjärn, Jmt</t>
+          <t>Bodtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519787.4697534219</v>
+        <v>519652</v>
       </c>
       <c r="R2" t="n">
-        <v>6998873.697896123</v>
+        <v>6998824</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98822793</v>
+        <v>98822807</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519828.7538666223</v>
+        <v>519754</v>
       </c>
       <c r="R3" t="n">
-        <v>6998940.475664497</v>
+        <v>6998858</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98822792</v>
+        <v>98822793</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519826.4714750989</v>
+        <v>519829</v>
       </c>
       <c r="R4" t="n">
-        <v>6998943.176992742</v>
+        <v>6998940</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98822807</v>
+        <v>98822805</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519754.4852618556</v>
+        <v>519793</v>
       </c>
       <c r="R5" t="n">
-        <v>6998857.657068099</v>
+        <v>6998959</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98822805</v>
+        <v>98822806</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519793.2943883753</v>
+        <v>519787</v>
       </c>
       <c r="R6" t="n">
-        <v>6998958.81333545</v>
+        <v>6998874</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1157,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98822792</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Älgflotjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>519826</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6998943</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25717-2024 artfynd.xlsx
+++ b/artfynd/A 25717-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822974</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822807</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822793</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822805</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822806</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822792</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>